--- a/fhir/finnish-scheduling/StructureDefinition-service-additional-information.xlsx
+++ b/fhir/finnish-scheduling/StructureDefinition-service-additional-information.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc2</t>
+    <t>2.0.0-rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-09T18:30:54+03:00</t>
+    <t>2025-08-27T16:15:51+03:00</t>
   </si>
   <si>
     <t>Publisher</t>
